--- a/gant/live/gantt_live.xlsx
+++ b/gant/live/gantt_live.xlsx
@@ -768,156 +768,160 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1176,2285 +1180,2285 @@
   <dimension ref="A2:AI46"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="10" style="0" width="4.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="10" style="1" width="4.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="42"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="3" t="n">
         <v>46303</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="5" t="s">
+      <c r="K5" s="5"/>
+      <c r="L5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="6" t="s">
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6" t="s">
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6" t="s">
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="AA5" s="6"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
-      <c r="AE5" s="4" t="s">
+      <c r="AA5" s="7"/>
+      <c r="AB5" s="7"/>
+      <c r="AC5" s="7"/>
+      <c r="AD5" s="7"/>
+      <c r="AE5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AF5" s="4"/>
-      <c r="AG5" s="4"/>
-      <c r="AH5" s="4"/>
-      <c r="AI5" s="7" t="s">
+      <c r="AF5" s="5"/>
+      <c r="AG5" s="5"/>
+      <c r="AH5" s="5"/>
+      <c r="AI5" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="M6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P6" s="9" t="s">
+      <c r="P6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="9" t="s">
+      <c r="Q6" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="R6" s="8" t="s">
+      <c r="R6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="S6" s="8" t="s">
+      <c r="S6" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="8" t="s">
+      <c r="T6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="U6" s="9" t="s">
+      <c r="U6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="V6" s="8" t="s">
+      <c r="V6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="W6" s="8" t="s">
+      <c r="W6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="X6" s="9" t="s">
+      <c r="X6" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="Y6" s="8" t="s">
+      <c r="Y6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="Z6" s="9" t="s">
+      <c r="Z6" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AA6" s="8" t="s">
+      <c r="AA6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AB6" s="8" t="s">
+      <c r="AB6" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="AC6" s="8" t="s">
+      <c r="AC6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="AD6" s="8" t="s">
+      <c r="AD6" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="AE6" s="8" t="s">
+      <c r="AE6" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="AF6" s="8" t="s">
+      <c r="AF6" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="AG6" s="8" t="s">
+      <c r="AG6" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="AH6" s="8" t="s">
+      <c r="AH6" s="9" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13" t="n">
+      <c r="C7" s="13"/>
+      <c r="D7" s="14" t="n">
         <v>46282</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <v>46304</v>
       </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="11" t="n">
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="12" t="n">
         <f aca="false">NETWORKDAYS(D7,E7,Holidays!$A$2:$A$1000)</f>
         <v>16</v>
       </c>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="14"/>
-      <c r="V7" s="12"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="14"/>
-      <c r="Y7" s="12"/>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="12"/>
-      <c r="AB7" s="12"/>
-      <c r="AC7" s="12"/>
-      <c r="AD7" s="12"/>
-      <c r="AE7" s="12"/>
-      <c r="AF7" s="12"/>
-      <c r="AG7" s="12"/>
-      <c r="AH7" s="12"/>
-      <c r="AI7" s="12"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="15"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="15"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="15"/>
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="13"/>
+      <c r="AC7" s="13"/>
+      <c r="AD7" s="13"/>
+      <c r="AE7" s="13"/>
+      <c r="AF7" s="13"/>
+      <c r="AG7" s="13"/>
+      <c r="AH7" s="13"/>
+      <c r="AI7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="18" t="n">
         <v>46282</v>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="17" t="n">
         <f aca="false">NETWORKDAYS(D8,E8,Holidays!$A$2:$A$1000)</f>
         <v>1</v>
       </c>
-      <c r="I8" s="18" t="s">
+      <c r="I8" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="16"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="19"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="16"/>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="19"/>
-      <c r="AA8" s="16"/>
-      <c r="AB8" s="16"/>
-      <c r="AC8" s="16"/>
-      <c r="AD8" s="16"/>
-      <c r="AE8" s="16"/>
-      <c r="AF8" s="16"/>
-      <c r="AG8" s="16"/>
-      <c r="AH8" s="16"/>
-      <c r="AI8" s="20" t="s">
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="17"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="17"/>
+      <c r="W8" s="17"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="17"/>
+      <c r="AB8" s="17"/>
+      <c r="AC8" s="17"/>
+      <c r="AD8" s="17"/>
+      <c r="AE8" s="17"/>
+      <c r="AF8" s="17"/>
+      <c r="AG8" s="17"/>
+      <c r="AH8" s="17"/>
+      <c r="AI8" s="21" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <v>46296</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <v>46296</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="18" t="n">
         <v>46296</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="18" t="n">
         <v>46296</v>
       </c>
-      <c r="H9" s="16" t="n">
+      <c r="H9" s="17" t="n">
         <f aca="false">NETWORKDAYS(D9,E9,Holidays!$A$2:$A$1000)</f>
         <v>1</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="J9" s="21"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="19"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="16"/>
-      <c r="Z9" s="19"/>
-      <c r="AA9" s="16"/>
-      <c r="AB9" s="16"/>
-      <c r="AC9" s="16"/>
-      <c r="AD9" s="16"/>
-      <c r="AE9" s="16"/>
-      <c r="AF9" s="16"/>
-      <c r="AG9" s="16"/>
-      <c r="AH9" s="16"/>
-      <c r="AI9" s="20" t="s">
+      <c r="J9" s="22"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="17"/>
+      <c r="AC9" s="17"/>
+      <c r="AD9" s="17"/>
+      <c r="AE9" s="17"/>
+      <c r="AF9" s="17"/>
+      <c r="AG9" s="17"/>
+      <c r="AH9" s="17"/>
+      <c r="AI9" s="21" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>46296</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <v>46297</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="18" t="n">
         <v>46296</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="18" t="n">
         <v>46297</v>
       </c>
-      <c r="H10" s="16" t="n">
+      <c r="H10" s="17" t="n">
         <f aca="false">NETWORKDAYS(D10,E10,Holidays!$A$2:$A$1000)</f>
         <v>2</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="19"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="19"/>
-      <c r="Y10" s="16"/>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="16"/>
-      <c r="AB10" s="16"/>
-      <c r="AC10" s="16"/>
-      <c r="AD10" s="16"/>
-      <c r="AE10" s="16"/>
-      <c r="AF10" s="16"/>
-      <c r="AG10" s="16"/>
-      <c r="AH10" s="16"/>
-      <c r="AI10" s="20" t="s">
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="17"/>
+      <c r="W10" s="17"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="17"/>
+      <c r="AB10" s="17"/>
+      <c r="AC10" s="17"/>
+      <c r="AD10" s="17"/>
+      <c r="AE10" s="17"/>
+      <c r="AF10" s="17"/>
+      <c r="AG10" s="17"/>
+      <c r="AH10" s="17"/>
+      <c r="AI10" s="21" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="18" t="n">
         <v>46297</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <v>46300</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="18" t="n">
         <v>46297</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="18" t="n">
         <v>46300</v>
       </c>
-      <c r="H11" s="16" t="n">
+      <c r="H11" s="17" t="n">
         <f aca="false">NETWORKDAYS(D11,E11,Holidays!$A$2:$A$1000)</f>
         <v>2</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="J11" s="16"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="19"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="16"/>
-      <c r="AB11" s="16"/>
-      <c r="AC11" s="16"/>
-      <c r="AD11" s="16"/>
-      <c r="AE11" s="16"/>
-      <c r="AF11" s="16"/>
-      <c r="AG11" s="16"/>
-      <c r="AH11" s="16"/>
-      <c r="AI11" s="20" t="s">
+      <c r="J11" s="17"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="17"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="17"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="17"/>
+      <c r="AC11" s="17"/>
+      <c r="AD11" s="17"/>
+      <c r="AE11" s="17"/>
+      <c r="AF11" s="17"/>
+      <c r="AG11" s="17"/>
+      <c r="AH11" s="17"/>
+      <c r="AI11" s="21" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>46297</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <v>46300</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="18" t="n">
         <v>46300</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="18" t="n">
         <v>46300</v>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="17" t="n">
         <f aca="false">NETWORKDAYS(D12,E12,Holidays!$A$2:$A$1000)</f>
         <v>2</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="I12" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="J12" s="16"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="19"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
-      <c r="X12" s="19"/>
-      <c r="Y12" s="16"/>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="16"/>
-      <c r="AB12" s="16"/>
-      <c r="AC12" s="16"/>
-      <c r="AD12" s="16"/>
-      <c r="AE12" s="16"/>
-      <c r="AF12" s="16"/>
-      <c r="AG12" s="16"/>
-      <c r="AH12" s="16"/>
-      <c r="AI12" s="20" t="s">
+      <c r="J12" s="17"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="17"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="20"/>
+      <c r="Y12" s="17"/>
+      <c r="Z12" s="20"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="17"/>
+      <c r="AC12" s="17"/>
+      <c r="AD12" s="17"/>
+      <c r="AE12" s="17"/>
+      <c r="AF12" s="17"/>
+      <c r="AG12" s="17"/>
+      <c r="AH12" s="17"/>
+      <c r="AI12" s="21" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>46303</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <v>46304</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="18" t="n">
         <v>46303</v>
       </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16" t="n">
+      <c r="G13" s="17"/>
+      <c r="H13" s="17" t="n">
         <f aca="false">NETWORKDAYS(D13,E13,Holidays!$A$2:$A$1000)</f>
         <v>2</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="19"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="19"/>
-      <c r="Y13" s="16"/>
-      <c r="Z13" s="19"/>
-      <c r="AA13" s="16"/>
-      <c r="AB13" s="16"/>
-      <c r="AC13" s="16"/>
-      <c r="AD13" s="16"/>
-      <c r="AE13" s="16"/>
-      <c r="AF13" s="16"/>
-      <c r="AG13" s="16"/>
-      <c r="AH13" s="16"/>
-      <c r="AI13" s="20" t="s">
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="17"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="17"/>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17"/>
+      <c r="AC13" s="17"/>
+      <c r="AD13" s="17"/>
+      <c r="AE13" s="17"/>
+      <c r="AF13" s="17"/>
+      <c r="AG13" s="17"/>
+      <c r="AH13" s="17"/>
+      <c r="AI13" s="21" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>46303</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <v>46304</v>
       </c>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16" t="n">
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17" t="n">
         <f aca="false">NETWORKDAYS(D14,E14,Holidays!$A$2:$A$1000)</f>
         <v>2</v>
       </c>
-      <c r="I14" s="18" t="s">
+      <c r="I14" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="19"/>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="19"/>
-      <c r="Y14" s="16"/>
-      <c r="Z14" s="19"/>
-      <c r="AA14" s="16"/>
-      <c r="AB14" s="16"/>
-      <c r="AC14" s="16"/>
-      <c r="AD14" s="16"/>
-      <c r="AE14" s="16"/>
-      <c r="AF14" s="16"/>
-      <c r="AG14" s="16"/>
-      <c r="AH14" s="16"/>
-      <c r="AI14" s="20" t="s">
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="17"/>
+      <c r="W14" s="17"/>
+      <c r="X14" s="20"/>
+      <c r="Y14" s="17"/>
+      <c r="Z14" s="20"/>
+      <c r="AA14" s="17"/>
+      <c r="AB14" s="17"/>
+      <c r="AC14" s="17"/>
+      <c r="AD14" s="17"/>
+      <c r="AE14" s="17"/>
+      <c r="AF14" s="17"/>
+      <c r="AG14" s="17"/>
+      <c r="AH14" s="17"/>
+      <c r="AI14" s="21" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13" t="n">
+      <c r="C15" s="13"/>
+      <c r="D15" s="14" t="n">
         <v>46296</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="14" t="n">
         <v>46317</v>
       </c>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="11" t="n">
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="12" t="n">
         <f aca="false">NETWORKDAYS(D15,E15,Holidays!$A$2:$A$1000)</f>
         <v>15</v>
       </c>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="12"/>
-      <c r="T15" s="12"/>
-      <c r="U15" s="14"/>
-      <c r="V15" s="12"/>
-      <c r="W15" s="12"/>
-      <c r="X15" s="14"/>
-      <c r="Y15" s="12"/>
-      <c r="Z15" s="14"/>
-      <c r="AA15" s="12"/>
-      <c r="AB15" s="12"/>
-      <c r="AC15" s="12"/>
-      <c r="AD15" s="12"/>
-      <c r="AE15" s="12"/>
-      <c r="AF15" s="12"/>
-      <c r="AG15" s="12"/>
-      <c r="AH15" s="12"/>
-      <c r="AI15" s="12"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="13"/>
+      <c r="U15" s="15"/>
+      <c r="V15" s="13"/>
+      <c r="W15" s="13"/>
+      <c r="X15" s="15"/>
+      <c r="Y15" s="13"/>
+      <c r="Z15" s="15"/>
+      <c r="AA15" s="13"/>
+      <c r="AB15" s="13"/>
+      <c r="AC15" s="13"/>
+      <c r="AD15" s="13"/>
+      <c r="AE15" s="13"/>
+      <c r="AF15" s="13"/>
+      <c r="AG15" s="13"/>
+      <c r="AH15" s="13"/>
+      <c r="AI15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <v>46296</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="18" t="n">
         <v>46300</v>
       </c>
-      <c r="F16" s="17" t="n">
+      <c r="F16" s="18" t="n">
         <v>46297</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G16" s="18" t="n">
         <v>46301</v>
       </c>
-      <c r="H16" s="16" t="n">
+      <c r="H16" s="17" t="n">
         <f aca="false">NETWORKDAYS(D16,E16,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I16" s="18" t="s">
+      <c r="I16" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="19"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="19"/>
-      <c r="Y16" s="16"/>
-      <c r="Z16" s="19"/>
-      <c r="AA16" s="16"/>
-      <c r="AB16" s="16"/>
-      <c r="AC16" s="16"/>
-      <c r="AD16" s="16"/>
-      <c r="AE16" s="16"/>
-      <c r="AF16" s="16"/>
-      <c r="AG16" s="16"/>
-      <c r="AH16" s="16"/>
-      <c r="AI16" s="20" t="s">
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="20"/>
+      <c r="V16" s="17"/>
+      <c r="W16" s="17"/>
+      <c r="X16" s="20"/>
+      <c r="Y16" s="17"/>
+      <c r="Z16" s="20"/>
+      <c r="AA16" s="17"/>
+      <c r="AB16" s="17"/>
+      <c r="AC16" s="17"/>
+      <c r="AD16" s="17"/>
+      <c r="AE16" s="17"/>
+      <c r="AF16" s="17"/>
+      <c r="AG16" s="17"/>
+      <c r="AH16" s="17"/>
+      <c r="AI16" s="21" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <v>46296</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="18" t="n">
         <v>46301</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="18" t="n">
         <v>46300</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="18" t="n">
         <v>46301</v>
       </c>
-      <c r="H17" s="16" t="n">
+      <c r="H17" s="17" t="n">
         <f aca="false">NETWORKDAYS(D17,E17,Holidays!$A$2:$A$1000)</f>
         <v>4</v>
       </c>
-      <c r="I17" s="18" t="s">
+      <c r="I17" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="16"/>
-      <c r="S17" s="16"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="19"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="19"/>
-      <c r="Y17" s="16"/>
-      <c r="Z17" s="19"/>
-      <c r="AA17" s="16"/>
-      <c r="AB17" s="16"/>
-      <c r="AC17" s="16"/>
-      <c r="AD17" s="16"/>
-      <c r="AE17" s="16"/>
-      <c r="AF17" s="16"/>
-      <c r="AG17" s="16"/>
-      <c r="AH17" s="16"/>
-      <c r="AI17" s="20" t="s">
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="17"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="17"/>
+      <c r="W17" s="17"/>
+      <c r="X17" s="20"/>
+      <c r="Y17" s="17"/>
+      <c r="Z17" s="20"/>
+      <c r="AA17" s="17"/>
+      <c r="AB17" s="17"/>
+      <c r="AC17" s="17"/>
+      <c r="AD17" s="17"/>
+      <c r="AE17" s="17"/>
+      <c r="AF17" s="17"/>
+      <c r="AG17" s="17"/>
+      <c r="AH17" s="17"/>
+      <c r="AI17" s="21" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="18" t="n">
         <v>46301</v>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="E18" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16" t="n">
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17" t="n">
         <f aca="false">NETWORKDAYS(D18,E18,Holidays!$A$2:$A$1000)</f>
         <v>5</v>
       </c>
-      <c r="I18" s="25" t="s">
+      <c r="I18" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="19"/>
-      <c r="V18" s="16"/>
-      <c r="W18" s="16"/>
-      <c r="X18" s="19"/>
-      <c r="Y18" s="16"/>
-      <c r="Z18" s="19"/>
-      <c r="AA18" s="16"/>
-      <c r="AB18" s="16"/>
-      <c r="AC18" s="16"/>
-      <c r="AD18" s="16"/>
-      <c r="AE18" s="16"/>
-      <c r="AF18" s="16"/>
-      <c r="AG18" s="16"/>
-      <c r="AH18" s="16"/>
-      <c r="AI18" s="20" t="s">
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="25"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="20"/>
+      <c r="V18" s="17"/>
+      <c r="W18" s="17"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="17"/>
+      <c r="Z18" s="20"/>
+      <c r="AA18" s="17"/>
+      <c r="AB18" s="17"/>
+      <c r="AC18" s="17"/>
+      <c r="AD18" s="17"/>
+      <c r="AE18" s="17"/>
+      <c r="AF18" s="17"/>
+      <c r="AG18" s="17"/>
+      <c r="AH18" s="17"/>
+      <c r="AI18" s="21" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="18" t="n">
         <v>46301</v>
       </c>
-      <c r="E19" s="17" t="n">
+      <c r="E19" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="F19" s="17" t="n">
+      <c r="F19" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="G19" s="17" t="n">
+      <c r="G19" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="H19" s="16" t="n">
+      <c r="H19" s="17" t="n">
         <f aca="false">NETWORKDAYS(D19,E19,Holidays!$A$2:$A$1000)</f>
         <v>5</v>
       </c>
-      <c r="I19" s="18" t="s">
+      <c r="I19" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="19"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="19"/>
-      <c r="Y19" s="16"/>
-      <c r="Z19" s="19"/>
-      <c r="AA19" s="16"/>
-      <c r="AB19" s="16"/>
-      <c r="AC19" s="16"/>
-      <c r="AD19" s="16"/>
-      <c r="AE19" s="16"/>
-      <c r="AF19" s="16"/>
-      <c r="AG19" s="16"/>
-      <c r="AH19" s="16"/>
-      <c r="AI19" s="20" t="s">
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="25"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="20"/>
+      <c r="V19" s="17"/>
+      <c r="W19" s="17"/>
+      <c r="X19" s="20"/>
+      <c r="Y19" s="17"/>
+      <c r="Z19" s="20"/>
+      <c r="AA19" s="17"/>
+      <c r="AB19" s="17"/>
+      <c r="AC19" s="17"/>
+      <c r="AD19" s="17"/>
+      <c r="AE19" s="17"/>
+      <c r="AF19" s="17"/>
+      <c r="AG19" s="17"/>
+      <c r="AH19" s="17"/>
+      <c r="AI19" s="21" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="18" t="n">
         <v>46301</v>
       </c>
-      <c r="E20" s="17" t="n">
+      <c r="E20" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16" t="n">
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17" t="n">
         <f aca="false">NETWORKDAYS(D20,E20,Holidays!$A$2:$A$1000)</f>
         <v>5</v>
       </c>
-      <c r="I20" s="25" t="s">
+      <c r="I20" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="16"/>
-      <c r="T20" s="16"/>
-      <c r="U20" s="19"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
-      <c r="X20" s="19"/>
-      <c r="Y20" s="16"/>
-      <c r="Z20" s="19"/>
-      <c r="AA20" s="16"/>
-      <c r="AB20" s="16"/>
-      <c r="AC20" s="16"/>
-      <c r="AD20" s="16"/>
-      <c r="AE20" s="16"/>
-      <c r="AF20" s="16"/>
-      <c r="AG20" s="16"/>
-      <c r="AH20" s="16"/>
-      <c r="AI20" s="20" t="s">
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="25"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="20"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="17"/>
+      <c r="X20" s="20"/>
+      <c r="Y20" s="17"/>
+      <c r="Z20" s="20"/>
+      <c r="AA20" s="17"/>
+      <c r="AB20" s="17"/>
+      <c r="AC20" s="17"/>
+      <c r="AD20" s="17"/>
+      <c r="AE20" s="17"/>
+      <c r="AF20" s="17"/>
+      <c r="AG20" s="17"/>
+      <c r="AH20" s="17"/>
+      <c r="AI20" s="21" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="18" t="n">
         <v>46301</v>
       </c>
-      <c r="E21" s="17" t="n">
+      <c r="E21" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16" t="n">
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17" t="n">
         <f aca="false">NETWORKDAYS(D21,E21,Holidays!$A$2:$A$1000)</f>
         <v>5</v>
       </c>
-      <c r="I21" s="18" t="s">
+      <c r="I21" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="16"/>
-      <c r="S21" s="16"/>
-      <c r="T21" s="16"/>
-      <c r="U21" s="19"/>
-      <c r="V21" s="16"/>
-      <c r="W21" s="16"/>
-      <c r="X21" s="19"/>
-      <c r="Y21" s="16"/>
-      <c r="Z21" s="19"/>
-      <c r="AA21" s="16"/>
-      <c r="AB21" s="16"/>
-      <c r="AC21" s="16"/>
-      <c r="AD21" s="16"/>
-      <c r="AE21" s="16"/>
-      <c r="AF21" s="16"/>
-      <c r="AG21" s="16"/>
-      <c r="AH21" s="16"/>
-      <c r="AI21" s="20" t="s">
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="24"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="20"/>
+      <c r="V21" s="17"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="20"/>
+      <c r="Y21" s="17"/>
+      <c r="Z21" s="20"/>
+      <c r="AA21" s="17"/>
+      <c r="AB21" s="17"/>
+      <c r="AC21" s="17"/>
+      <c r="AD21" s="17"/>
+      <c r="AE21" s="17"/>
+      <c r="AF21" s="17"/>
+      <c r="AG21" s="17"/>
+      <c r="AH21" s="17"/>
+      <c r="AI21" s="21" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="18" t="n">
         <v>46296</v>
       </c>
-      <c r="E22" s="17" t="n">
+      <c r="E22" s="18" t="n">
         <v>46317</v>
       </c>
-      <c r="F22" s="17" t="n">
-        <v>46296</v>
-      </c>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16" t="n">
+      <c r="F22" s="18" t="n">
+        <v>46310</v>
+      </c>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17" t="n">
         <f aca="false">NETWORKDAYS(D22,E22,Holidays!$A$2:$A$1000)</f>
         <v>15</v>
       </c>
-      <c r="I22" s="26" t="s">
+      <c r="I22" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="24"/>
-      <c r="Q22" s="24"/>
-      <c r="R22" s="23"/>
-      <c r="S22" s="23"/>
-      <c r="T22" s="23"/>
-      <c r="U22" s="24"/>
-      <c r="V22" s="23"/>
-      <c r="W22" s="23"/>
-      <c r="X22" s="24"/>
-      <c r="Y22" s="16"/>
-      <c r="Z22" s="19"/>
-      <c r="AA22" s="16"/>
-      <c r="AB22" s="16"/>
-      <c r="AC22" s="16"/>
-      <c r="AD22" s="16"/>
-      <c r="AE22" s="16"/>
-      <c r="AF22" s="16"/>
-      <c r="AG22" s="16"/>
-      <c r="AH22" s="16"/>
-      <c r="AI22" s="20" t="s">
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="25"/>
+      <c r="Q22" s="25"/>
+      <c r="R22" s="24"/>
+      <c r="S22" s="24"/>
+      <c r="T22" s="24"/>
+      <c r="U22" s="25"/>
+      <c r="V22" s="24"/>
+      <c r="W22" s="24"/>
+      <c r="X22" s="25"/>
+      <c r="Y22" s="17"/>
+      <c r="Z22" s="20"/>
+      <c r="AA22" s="17"/>
+      <c r="AB22" s="17"/>
+      <c r="AC22" s="17"/>
+      <c r="AD22" s="17"/>
+      <c r="AE22" s="17"/>
+      <c r="AF22" s="17"/>
+      <c r="AG22" s="17"/>
+      <c r="AH22" s="17"/>
+      <c r="AI22" s="21" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="13" t="n">
+      <c r="C23" s="13"/>
+      <c r="D23" s="14" t="n">
         <v>46308</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="14" t="n">
         <v>46317</v>
       </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="11" t="n">
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="12" t="n">
         <f aca="false">NETWORKDAYS(D23,E23,Holidays!$A$2:$A$1000)</f>
         <v>8</v>
       </c>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="14"/>
-      <c r="R23" s="12"/>
-      <c r="S23" s="12"/>
-      <c r="T23" s="12"/>
-      <c r="U23" s="14"/>
-      <c r="V23" s="12"/>
-      <c r="W23" s="12"/>
-      <c r="X23" s="14"/>
-      <c r="Y23" s="12"/>
-      <c r="Z23" s="14"/>
-      <c r="AA23" s="12"/>
-      <c r="AB23" s="12"/>
-      <c r="AC23" s="12"/>
-      <c r="AD23" s="12"/>
-      <c r="AE23" s="12"/>
-      <c r="AF23" s="12"/>
-      <c r="AG23" s="12"/>
-      <c r="AH23" s="12"/>
-      <c r="AI23" s="12"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="15"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="13"/>
+      <c r="T23" s="13"/>
+      <c r="U23" s="15"/>
+      <c r="V23" s="13"/>
+      <c r="W23" s="13"/>
+      <c r="X23" s="15"/>
+      <c r="Y23" s="13"/>
+      <c r="Z23" s="15"/>
+      <c r="AA23" s="13"/>
+      <c r="AB23" s="13"/>
+      <c r="AC23" s="13"/>
+      <c r="AD23" s="13"/>
+      <c r="AE23" s="13"/>
+      <c r="AF23" s="13"/>
+      <c r="AG23" s="13"/>
+      <c r="AH23" s="13"/>
+      <c r="AI23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="E24" s="17" t="n">
+      <c r="E24" s="18" t="n">
         <v>46310</v>
       </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16" t="n">
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17" t="n">
         <f aca="false">NETWORKDAYS(D24,E24,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I24" s="18" t="s">
+      <c r="I24" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="27"/>
-      <c r="R24" s="28"/>
-      <c r="S24" s="28"/>
-      <c r="T24" s="16"/>
-      <c r="U24" s="19"/>
-      <c r="V24" s="16"/>
-      <c r="W24" s="16"/>
-      <c r="X24" s="19"/>
-      <c r="Y24" s="16"/>
-      <c r="Z24" s="19"/>
-      <c r="AA24" s="16"/>
-      <c r="AB24" s="16"/>
-      <c r="AC24" s="16"/>
-      <c r="AD24" s="16"/>
-      <c r="AE24" s="16"/>
-      <c r="AF24" s="16"/>
-      <c r="AG24" s="16"/>
-      <c r="AH24" s="16"/>
-      <c r="AI24" s="20" t="s">
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="28"/>
+      <c r="R24" s="29"/>
+      <c r="S24" s="29"/>
+      <c r="T24" s="17"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="17"/>
+      <c r="W24" s="17"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="17"/>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="17"/>
+      <c r="AB24" s="17"/>
+      <c r="AC24" s="17"/>
+      <c r="AD24" s="17"/>
+      <c r="AE24" s="17"/>
+      <c r="AF24" s="17"/>
+      <c r="AG24" s="17"/>
+      <c r="AH24" s="17"/>
+      <c r="AI24" s="21" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="18" t="n">
         <v>46310</v>
       </c>
-      <c r="E25" s="17" t="n">
+      <c r="E25" s="18" t="n">
         <v>46314</v>
       </c>
-      <c r="F25" s="17" t="n">
+      <c r="F25" s="18" t="n">
         <v>46310</v>
       </c>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16" t="n">
+      <c r="G25" s="17"/>
+      <c r="H25" s="17" t="n">
         <f aca="false">NETWORKDAYS(D25,E25,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I25" s="26" t="s">
+      <c r="I25" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="16"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="28"/>
-      <c r="U25" s="27"/>
-      <c r="V25" s="16"/>
-      <c r="W25" s="16"/>
-      <c r="X25" s="19"/>
-      <c r="Y25" s="16"/>
-      <c r="Z25" s="19"/>
-      <c r="AA25" s="16"/>
-      <c r="AB25" s="16"/>
-      <c r="AC25" s="16"/>
-      <c r="AD25" s="16"/>
-      <c r="AE25" s="16"/>
-      <c r="AF25" s="16"/>
-      <c r="AG25" s="16"/>
-      <c r="AH25" s="16"/>
-      <c r="AI25" s="20" t="s">
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="29"/>
+      <c r="U25" s="28"/>
+      <c r="V25" s="17"/>
+      <c r="W25" s="17"/>
+      <c r="X25" s="20"/>
+      <c r="Y25" s="17"/>
+      <c r="Z25" s="20"/>
+      <c r="AA25" s="17"/>
+      <c r="AB25" s="17"/>
+      <c r="AC25" s="17"/>
+      <c r="AD25" s="17"/>
+      <c r="AE25" s="17"/>
+      <c r="AF25" s="17"/>
+      <c r="AG25" s="17"/>
+      <c r="AH25" s="17"/>
+      <c r="AI25" s="21" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="E26" s="17" t="n">
+      <c r="E26" s="18" t="n">
         <v>46314</v>
       </c>
-      <c r="F26" s="17" t="n">
+      <c r="F26" s="18" t="n">
         <v>46310</v>
       </c>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16" t="n">
+      <c r="G26" s="17"/>
+      <c r="H26" s="17" t="n">
         <f aca="false">NETWORKDAYS(D26,E26,Holidays!$A$2:$A$1000)</f>
         <v>5</v>
       </c>
-      <c r="I26" s="26" t="s">
+      <c r="I26" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="27"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="28"/>
-      <c r="T26" s="28"/>
-      <c r="U26" s="27"/>
-      <c r="V26" s="16"/>
-      <c r="W26" s="16"/>
-      <c r="X26" s="19"/>
-      <c r="Y26" s="16"/>
-      <c r="Z26" s="19"/>
-      <c r="AA26" s="16"/>
-      <c r="AB26" s="16"/>
-      <c r="AC26" s="16"/>
-      <c r="AD26" s="16"/>
-      <c r="AE26" s="16"/>
-      <c r="AF26" s="16"/>
-      <c r="AG26" s="16"/>
-      <c r="AH26" s="16"/>
-      <c r="AI26" s="20" t="s">
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="28"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="28"/>
+      <c r="V26" s="17"/>
+      <c r="W26" s="17"/>
+      <c r="X26" s="20"/>
+      <c r="Y26" s="17"/>
+      <c r="Z26" s="20"/>
+      <c r="AA26" s="17"/>
+      <c r="AB26" s="17"/>
+      <c r="AC26" s="17"/>
+      <c r="AD26" s="17"/>
+      <c r="AE26" s="17"/>
+      <c r="AF26" s="17"/>
+      <c r="AG26" s="17"/>
+      <c r="AH26" s="17"/>
+      <c r="AI26" s="21" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="18" t="n">
         <v>46315</v>
       </c>
-      <c r="E27" s="17" t="n">
+      <c r="E27" s="18" t="n">
         <v>46317</v>
       </c>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16" t="n">
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17" t="n">
         <f aca="false">NETWORKDAYS(D27,E27,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I27" s="29" t="s">
+      <c r="I27" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="16"/>
-      <c r="S27" s="16"/>
-      <c r="T27" s="16"/>
-      <c r="U27" s="19"/>
-      <c r="V27" s="28"/>
-      <c r="W27" s="28"/>
-      <c r="X27" s="27"/>
-      <c r="Y27" s="16"/>
-      <c r="Z27" s="19"/>
-      <c r="AA27" s="16"/>
-      <c r="AB27" s="16"/>
-      <c r="AC27" s="16"/>
-      <c r="AD27" s="16"/>
-      <c r="AE27" s="16"/>
-      <c r="AF27" s="16"/>
-      <c r="AG27" s="16"/>
-      <c r="AH27" s="16"/>
-      <c r="AI27" s="20" t="s">
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17"/>
+      <c r="T27" s="17"/>
+      <c r="U27" s="20"/>
+      <c r="V27" s="29"/>
+      <c r="W27" s="29"/>
+      <c r="X27" s="28"/>
+      <c r="Y27" s="17"/>
+      <c r="Z27" s="20"/>
+      <c r="AA27" s="17"/>
+      <c r="AB27" s="17"/>
+      <c r="AC27" s="17"/>
+      <c r="AD27" s="17"/>
+      <c r="AE27" s="17"/>
+      <c r="AF27" s="17"/>
+      <c r="AG27" s="17"/>
+      <c r="AH27" s="17"/>
+      <c r="AI27" s="21" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="E28" s="17" t="n">
+      <c r="E28" s="18" t="n">
         <v>46314</v>
       </c>
-      <c r="F28" s="17" t="n">
+      <c r="F28" s="18" t="n">
         <v>46310</v>
       </c>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16" t="n">
+      <c r="G28" s="17"/>
+      <c r="H28" s="17" t="n">
         <f aca="false">NETWORKDAYS(D28,E28,Holidays!$A$2:$A$1000)</f>
         <v>5</v>
       </c>
-      <c r="I28" s="26" t="s">
+      <c r="I28" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="27"/>
-      <c r="R28" s="28"/>
-      <c r="S28" s="28"/>
-      <c r="T28" s="28"/>
-      <c r="U28" s="27"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="19"/>
-      <c r="Y28" s="16"/>
-      <c r="Z28" s="19"/>
-      <c r="AA28" s="16"/>
-      <c r="AB28" s="16"/>
-      <c r="AC28" s="16"/>
-      <c r="AD28" s="16"/>
-      <c r="AE28" s="16"/>
-      <c r="AF28" s="16"/>
-      <c r="AG28" s="16"/>
-      <c r="AH28" s="16"/>
-      <c r="AI28" s="20" t="s">
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="28"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="28"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="20"/>
+      <c r="Y28" s="17"/>
+      <c r="Z28" s="20"/>
+      <c r="AA28" s="17"/>
+      <c r="AB28" s="17"/>
+      <c r="AC28" s="17"/>
+      <c r="AD28" s="17"/>
+      <c r="AE28" s="17"/>
+      <c r="AF28" s="17"/>
+      <c r="AG28" s="17"/>
+      <c r="AH28" s="17"/>
+      <c r="AI28" s="21" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="18" t="n">
         <v>46315</v>
       </c>
-      <c r="E29" s="17" t="n">
+      <c r="E29" s="18" t="n">
         <v>46317</v>
       </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16" t="n">
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17" t="n">
         <f aca="false">NETWORKDAYS(D29,E29,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I29" s="29" t="s">
+      <c r="I29" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="16"/>
-      <c r="O29" s="16"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="16"/>
-      <c r="S29" s="16"/>
-      <c r="T29" s="16"/>
-      <c r="U29" s="19"/>
-      <c r="V29" s="28"/>
-      <c r="W29" s="28"/>
-      <c r="X29" s="27"/>
-      <c r="Y29" s="16"/>
-      <c r="Z29" s="19"/>
-      <c r="AA29" s="16"/>
-      <c r="AB29" s="16"/>
-      <c r="AC29" s="16"/>
-      <c r="AD29" s="16"/>
-      <c r="AE29" s="16"/>
-      <c r="AF29" s="16"/>
-      <c r="AG29" s="16"/>
-      <c r="AH29" s="16"/>
-      <c r="AI29" s="20" t="s">
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="29"/>
+      <c r="X29" s="28"/>
+      <c r="Y29" s="17"/>
+      <c r="Z29" s="20"/>
+      <c r="AA29" s="17"/>
+      <c r="AB29" s="17"/>
+      <c r="AC29" s="17"/>
+      <c r="AD29" s="17"/>
+      <c r="AE29" s="17"/>
+      <c r="AF29" s="17"/>
+      <c r="AG29" s="17"/>
+      <c r="AH29" s="17"/>
+      <c r="AI29" s="21" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="13" t="n">
+      <c r="C30" s="13"/>
+      <c r="D30" s="14" t="n">
         <v>46311</v>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E30" s="14" t="n">
         <v>46321</v>
       </c>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="11" t="n">
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="12" t="n">
         <f aca="false">NETWORKDAYS(D30,E30,Holidays!$A$2:$A$1000)</f>
         <v>7</v>
       </c>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="14"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="12"/>
-      <c r="U30" s="14"/>
-      <c r="V30" s="12"/>
-      <c r="W30" s="12"/>
-      <c r="X30" s="14"/>
-      <c r="Y30" s="12"/>
-      <c r="Z30" s="14"/>
-      <c r="AA30" s="12"/>
-      <c r="AB30" s="12"/>
-      <c r="AC30" s="12"/>
-      <c r="AD30" s="12"/>
-      <c r="AE30" s="12"/>
-      <c r="AF30" s="12"/>
-      <c r="AG30" s="12"/>
-      <c r="AH30" s="12"/>
-      <c r="AI30" s="12"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15"/>
+      <c r="R30" s="13"/>
+      <c r="S30" s="13"/>
+      <c r="T30" s="13"/>
+      <c r="U30" s="15"/>
+      <c r="V30" s="13"/>
+      <c r="W30" s="13"/>
+      <c r="X30" s="15"/>
+      <c r="Y30" s="13"/>
+      <c r="Z30" s="15"/>
+      <c r="AA30" s="13"/>
+      <c r="AB30" s="13"/>
+      <c r="AC30" s="13"/>
+      <c r="AD30" s="13"/>
+      <c r="AE30" s="13"/>
+      <c r="AF30" s="13"/>
+      <c r="AG30" s="13"/>
+      <c r="AH30" s="13"/>
+      <c r="AI30" s="13"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="18" t="n">
         <v>46315</v>
       </c>
-      <c r="E31" s="17" t="n">
+      <c r="E31" s="18" t="n">
         <v>46315</v>
       </c>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16" t="n">
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17" t="n">
         <f aca="false">NETWORKDAYS(D31,E31,Holidays!$A$2:$A$1000)</f>
         <v>1</v>
       </c>
-      <c r="I31" s="29" t="s">
+      <c r="I31" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="16"/>
-      <c r="P31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="16"/>
-      <c r="S31" s="16"/>
-      <c r="T31" s="16"/>
-      <c r="U31" s="19"/>
-      <c r="V31" s="30"/>
-      <c r="W31" s="16"/>
-      <c r="X31" s="19"/>
-      <c r="Y31" s="16"/>
-      <c r="Z31" s="19"/>
-      <c r="AA31" s="16"/>
-      <c r="AB31" s="16"/>
-      <c r="AC31" s="16"/>
-      <c r="AD31" s="16"/>
-      <c r="AE31" s="16"/>
-      <c r="AF31" s="16"/>
-      <c r="AG31" s="16"/>
-      <c r="AH31" s="16"/>
-      <c r="AI31" s="20"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="17"/>
+      <c r="T31" s="17"/>
+      <c r="U31" s="20"/>
+      <c r="V31" s="31"/>
+      <c r="W31" s="17"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="17"/>
+      <c r="Z31" s="20"/>
+      <c r="AA31" s="17"/>
+      <c r="AB31" s="17"/>
+      <c r="AC31" s="17"/>
+      <c r="AD31" s="17"/>
+      <c r="AE31" s="17"/>
+      <c r="AF31" s="17"/>
+      <c r="AG31" s="17"/>
+      <c r="AH31" s="17"/>
+      <c r="AI31" s="21"/>
     </row>
     <row r="32" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="18" t="n">
         <v>46311</v>
       </c>
-      <c r="E32" s="17" t="n">
+      <c r="E32" s="18" t="n">
         <v>46311</v>
       </c>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16" t="n">
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17" t="n">
         <f aca="false">NETWORKDAYS(D32,E32,Holidays!$A$2:$A$1000)</f>
         <v>1</v>
       </c>
-      <c r="I32" s="29" t="s">
+      <c r="I32" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="16"/>
-      <c r="S32" s="16"/>
-      <c r="T32" s="30"/>
-      <c r="U32" s="19"/>
-      <c r="V32" s="16"/>
-      <c r="W32" s="16"/>
-      <c r="X32" s="19"/>
-      <c r="Y32" s="16"/>
-      <c r="Z32" s="19"/>
-      <c r="AA32" s="16"/>
-      <c r="AB32" s="16"/>
-      <c r="AC32" s="16"/>
-      <c r="AD32" s="16"/>
-      <c r="AE32" s="16"/>
-      <c r="AF32" s="16"/>
-      <c r="AG32" s="16"/>
-      <c r="AH32" s="16"/>
-      <c r="AI32" s="20" t="s">
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="17"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="20"/>
+      <c r="V32" s="17"/>
+      <c r="W32" s="17"/>
+      <c r="X32" s="20"/>
+      <c r="Y32" s="17"/>
+      <c r="Z32" s="20"/>
+      <c r="AA32" s="17"/>
+      <c r="AB32" s="17"/>
+      <c r="AC32" s="17"/>
+      <c r="AD32" s="17"/>
+      <c r="AE32" s="17"/>
+      <c r="AF32" s="17"/>
+      <c r="AG32" s="17"/>
+      <c r="AH32" s="17"/>
+      <c r="AI32" s="21" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="18" t="n">
         <v>46314</v>
       </c>
-      <c r="E33" s="17" t="n">
+      <c r="E33" s="18" t="n">
         <v>46317</v>
       </c>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16" t="n">
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17" t="n">
         <f aca="false">NETWORKDAYS(D33,E33,Holidays!$A$2:$A$1000)</f>
         <v>4</v>
       </c>
-      <c r="I33" s="29" t="s">
+      <c r="I33" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="J33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="16"/>
-      <c r="O33" s="16"/>
-      <c r="P33" s="19"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="16"/>
-      <c r="S33" s="16"/>
-      <c r="T33" s="16"/>
-      <c r="U33" s="31"/>
-      <c r="V33" s="30"/>
-      <c r="W33" s="30"/>
-      <c r="X33" s="31"/>
-      <c r="Y33" s="16"/>
-      <c r="Z33" s="19"/>
-      <c r="AA33" s="16"/>
-      <c r="AB33" s="16"/>
-      <c r="AC33" s="16"/>
-      <c r="AD33" s="16"/>
-      <c r="AE33" s="16"/>
-      <c r="AF33" s="16"/>
-      <c r="AG33" s="16"/>
-      <c r="AH33" s="16"/>
-      <c r="AI33" s="20"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="20"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="17"/>
+      <c r="U33" s="32"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="32"/>
+      <c r="Y33" s="17"/>
+      <c r="Z33" s="20"/>
+      <c r="AA33" s="17"/>
+      <c r="AB33" s="17"/>
+      <c r="AC33" s="17"/>
+      <c r="AD33" s="17"/>
+      <c r="AE33" s="17"/>
+      <c r="AF33" s="17"/>
+      <c r="AG33" s="17"/>
+      <c r="AH33" s="17"/>
+      <c r="AI33" s="21"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="18" t="n">
         <v>46315</v>
       </c>
-      <c r="E34" s="17" t="n">
+      <c r="E34" s="18" t="n">
         <v>46317</v>
       </c>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16" t="n">
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17" t="n">
         <f aca="false">NETWORKDAYS(D34,E34,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I34" s="29" t="s">
+      <c r="I34" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="16"/>
-      <c r="O34" s="16"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="16"/>
-      <c r="S34" s="16"/>
-      <c r="T34" s="16"/>
-      <c r="U34" s="19"/>
-      <c r="V34" s="30"/>
-      <c r="W34" s="30"/>
-      <c r="X34" s="31"/>
-      <c r="Y34" s="16"/>
-      <c r="Z34" s="19"/>
-      <c r="AA34" s="16"/>
-      <c r="AB34" s="16"/>
-      <c r="AC34" s="16"/>
-      <c r="AD34" s="16"/>
-      <c r="AE34" s="16"/>
-      <c r="AF34" s="16"/>
-      <c r="AG34" s="16"/>
-      <c r="AH34" s="16"/>
-      <c r="AI34" s="20"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="20"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="20"/>
+      <c r="V34" s="31"/>
+      <c r="W34" s="31"/>
+      <c r="X34" s="32"/>
+      <c r="Y34" s="17"/>
+      <c r="Z34" s="20"/>
+      <c r="AA34" s="17"/>
+      <c r="AB34" s="17"/>
+      <c r="AC34" s="17"/>
+      <c r="AD34" s="17"/>
+      <c r="AE34" s="17"/>
+      <c r="AF34" s="17"/>
+      <c r="AG34" s="17"/>
+      <c r="AH34" s="17"/>
+      <c r="AI34" s="21"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="18" t="n">
         <v>46315</v>
       </c>
-      <c r="E35" s="17" t="n">
+      <c r="E35" s="18" t="n">
         <v>46317</v>
       </c>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16" t="n">
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17" t="n">
         <f aca="false">NETWORKDAYS(D35,E35,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I35" s="29" t="s">
+      <c r="I35" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="16"/>
-      <c r="O35" s="16"/>
-      <c r="P35" s="19"/>
-      <c r="Q35" s="19"/>
-      <c r="R35" s="16"/>
-      <c r="S35" s="16"/>
-      <c r="T35" s="16"/>
-      <c r="U35" s="19"/>
-      <c r="V35" s="30"/>
-      <c r="W35" s="30"/>
-      <c r="X35" s="31"/>
-      <c r="Y35" s="16"/>
-      <c r="Z35" s="19"/>
-      <c r="AA35" s="16"/>
-      <c r="AB35" s="16"/>
-      <c r="AC35" s="16"/>
-      <c r="AD35" s="16"/>
-      <c r="AE35" s="16"/>
-      <c r="AF35" s="16"/>
-      <c r="AG35" s="16"/>
-      <c r="AH35" s="16"/>
-      <c r="AI35" s="20"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="20"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="20"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="20"/>
+      <c r="V35" s="31"/>
+      <c r="W35" s="31"/>
+      <c r="X35" s="32"/>
+      <c r="Y35" s="17"/>
+      <c r="Z35" s="20"/>
+      <c r="AA35" s="17"/>
+      <c r="AB35" s="17"/>
+      <c r="AC35" s="17"/>
+      <c r="AD35" s="17"/>
+      <c r="AE35" s="17"/>
+      <c r="AF35" s="17"/>
+      <c r="AG35" s="17"/>
+      <c r="AH35" s="17"/>
+      <c r="AI35" s="21"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D36" s="17" t="n">
+      <c r="D36" s="18" t="n">
         <v>46315</v>
       </c>
-      <c r="E36" s="17" t="n">
+      <c r="E36" s="18" t="n">
         <v>46317</v>
       </c>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16" t="n">
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17" t="n">
         <f aca="false">NETWORKDAYS(D36,E36,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I36" s="29" t="s">
+      <c r="I36" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="16"/>
-      <c r="O36" s="16"/>
-      <c r="P36" s="19"/>
-      <c r="Q36" s="19"/>
-      <c r="R36" s="16"/>
-      <c r="S36" s="16"/>
-      <c r="T36" s="16"/>
-      <c r="U36" s="19"/>
-      <c r="V36" s="30"/>
-      <c r="W36" s="30"/>
-      <c r="X36" s="31"/>
-      <c r="Y36" s="16"/>
-      <c r="Z36" s="19"/>
-      <c r="AA36" s="16"/>
-      <c r="AB36" s="16"/>
-      <c r="AC36" s="16"/>
-      <c r="AD36" s="16"/>
-      <c r="AE36" s="16"/>
-      <c r="AF36" s="16"/>
-      <c r="AG36" s="16"/>
-      <c r="AH36" s="16"/>
-      <c r="AI36" s="20"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="20"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20"/>
+      <c r="R36" s="17"/>
+      <c r="S36" s="17"/>
+      <c r="T36" s="17"/>
+      <c r="U36" s="20"/>
+      <c r="V36" s="31"/>
+      <c r="W36" s="31"/>
+      <c r="X36" s="32"/>
+      <c r="Y36" s="17"/>
+      <c r="Z36" s="20"/>
+      <c r="AA36" s="17"/>
+      <c r="AB36" s="17"/>
+      <c r="AC36" s="17"/>
+      <c r="AD36" s="17"/>
+      <c r="AE36" s="17"/>
+      <c r="AF36" s="17"/>
+      <c r="AG36" s="17"/>
+      <c r="AH36" s="17"/>
+      <c r="AI36" s="21"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D37" s="17" t="n">
+      <c r="D37" s="18" t="n">
         <v>46317</v>
       </c>
-      <c r="E37" s="17" t="n">
+      <c r="E37" s="18" t="n">
         <v>46318</v>
       </c>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16" t="n">
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17" t="n">
         <f aca="false">NETWORKDAYS(D37,E37,Holidays!$A$2:$A$1000)</f>
         <v>2</v>
       </c>
-      <c r="I37" s="29" t="s">
+      <c r="I37" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="J37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="19"/>
-      <c r="N37" s="16"/>
-      <c r="O37" s="16"/>
-      <c r="P37" s="19"/>
-      <c r="Q37" s="19"/>
-      <c r="R37" s="16"/>
-      <c r="S37" s="16"/>
-      <c r="T37" s="16"/>
-      <c r="U37" s="19"/>
-      <c r="V37" s="16"/>
-      <c r="W37" s="16"/>
-      <c r="X37" s="31"/>
-      <c r="Y37" s="30"/>
-      <c r="Z37" s="19"/>
-      <c r="AA37" s="16"/>
-      <c r="AB37" s="16"/>
-      <c r="AC37" s="16"/>
-      <c r="AD37" s="16"/>
-      <c r="AE37" s="16"/>
-      <c r="AF37" s="16"/>
-      <c r="AG37" s="16"/>
-      <c r="AH37" s="16"/>
-      <c r="AI37" s="20"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="20"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="20"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="20"/>
+      <c r="V37" s="17"/>
+      <c r="W37" s="17"/>
+      <c r="X37" s="32"/>
+      <c r="Y37" s="31"/>
+      <c r="Z37" s="20"/>
+      <c r="AA37" s="17"/>
+      <c r="AB37" s="17"/>
+      <c r="AC37" s="17"/>
+      <c r="AD37" s="17"/>
+      <c r="AE37" s="17"/>
+      <c r="AF37" s="17"/>
+      <c r="AG37" s="17"/>
+      <c r="AH37" s="17"/>
+      <c r="AI37" s="21"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="18" t="n">
         <v>46318</v>
       </c>
-      <c r="E38" s="17" t="n">
+      <c r="E38" s="18" t="n">
         <v>46318</v>
       </c>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16" t="n">
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17" t="n">
         <f aca="false">NETWORKDAYS(D38,E38,Holidays!$A$2:$A$1000)</f>
         <v>1</v>
       </c>
-      <c r="I38" s="29" t="s">
+      <c r="I38" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-      <c r="P38" s="19"/>
-      <c r="Q38" s="19"/>
-      <c r="R38" s="16"/>
-      <c r="S38" s="16"/>
-      <c r="T38" s="16"/>
-      <c r="U38" s="19"/>
-      <c r="V38" s="16"/>
-      <c r="W38" s="16"/>
-      <c r="X38" s="19"/>
-      <c r="Y38" s="30"/>
-      <c r="Z38" s="19"/>
-      <c r="AA38" s="16"/>
-      <c r="AB38" s="16"/>
-      <c r="AC38" s="16"/>
-      <c r="AD38" s="16"/>
-      <c r="AE38" s="16"/>
-      <c r="AF38" s="16"/>
-      <c r="AG38" s="16"/>
-      <c r="AH38" s="16"/>
-      <c r="AI38" s="20"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="20"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="20"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="17"/>
+      <c r="U38" s="20"/>
+      <c r="V38" s="17"/>
+      <c r="W38" s="17"/>
+      <c r="X38" s="20"/>
+      <c r="Y38" s="31"/>
+      <c r="Z38" s="20"/>
+      <c r="AA38" s="17"/>
+      <c r="AB38" s="17"/>
+      <c r="AC38" s="17"/>
+      <c r="AD38" s="17"/>
+      <c r="AE38" s="17"/>
+      <c r="AF38" s="17"/>
+      <c r="AG38" s="17"/>
+      <c r="AH38" s="17"/>
+      <c r="AI38" s="21"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D39" s="17" t="n">
+      <c r="D39" s="18" t="n">
         <v>46321</v>
       </c>
-      <c r="E39" s="17" t="n">
+      <c r="E39" s="18" t="n">
         <v>46321</v>
       </c>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16" t="n">
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17" t="n">
         <f aca="false">NETWORKDAYS(D39,E39,Holidays!$A$2:$A$1000)</f>
         <v>1</v>
       </c>
-      <c r="I39" s="29" t="s">
+      <c r="I39" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="19"/>
-      <c r="Q39" s="19"/>
-      <c r="R39" s="16"/>
-      <c r="S39" s="16"/>
-      <c r="T39" s="16"/>
-      <c r="U39" s="19"/>
-      <c r="V39" s="16"/>
-      <c r="W39" s="16"/>
-      <c r="X39" s="19"/>
-      <c r="Y39" s="16"/>
-      <c r="Z39" s="31"/>
-      <c r="AA39" s="16"/>
-      <c r="AB39" s="16"/>
-      <c r="AC39" s="16"/>
-      <c r="AD39" s="16"/>
-      <c r="AE39" s="16"/>
-      <c r="AF39" s="16"/>
-      <c r="AG39" s="16"/>
-      <c r="AH39" s="16"/>
-      <c r="AI39" s="20"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="20"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="17"/>
+      <c r="S39" s="17"/>
+      <c r="T39" s="17"/>
+      <c r="U39" s="20"/>
+      <c r="V39" s="17"/>
+      <c r="W39" s="17"/>
+      <c r="X39" s="20"/>
+      <c r="Y39" s="17"/>
+      <c r="Z39" s="32"/>
+      <c r="AA39" s="17"/>
+      <c r="AB39" s="17"/>
+      <c r="AC39" s="17"/>
+      <c r="AD39" s="17"/>
+      <c r="AE39" s="17"/>
+      <c r="AF39" s="17"/>
+      <c r="AG39" s="17"/>
+      <c r="AH39" s="17"/>
+      <c r="AI39" s="21"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="C40" s="12"/>
-      <c r="D40" s="13" t="n">
+      <c r="C40" s="13"/>
+      <c r="D40" s="14" t="n">
         <v>46322</v>
       </c>
-      <c r="E40" s="13" t="n">
+      <c r="E40" s="14" t="n">
         <v>46331</v>
       </c>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="11" t="n">
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="12" t="n">
         <f aca="false">NETWORKDAYS(D40,E40,Holidays!$A$2:$A$1000)</f>
         <v>8</v>
       </c>
-      <c r="I40" s="12"/>
-      <c r="J40" s="12"/>
-      <c r="K40" s="12"/>
-      <c r="L40" s="12"/>
-      <c r="M40" s="14"/>
-      <c r="N40" s="12"/>
-      <c r="O40" s="12"/>
-      <c r="P40" s="14"/>
-      <c r="Q40" s="14"/>
-      <c r="R40" s="12"/>
-      <c r="S40" s="12"/>
-      <c r="T40" s="12"/>
-      <c r="U40" s="14"/>
-      <c r="V40" s="12"/>
-      <c r="W40" s="12"/>
-      <c r="X40" s="14"/>
-      <c r="Y40" s="12"/>
-      <c r="Z40" s="14"/>
-      <c r="AA40" s="12"/>
-      <c r="AB40" s="12"/>
-      <c r="AC40" s="12"/>
-      <c r="AD40" s="12"/>
-      <c r="AE40" s="12"/>
-      <c r="AF40" s="12"/>
-      <c r="AG40" s="12"/>
-      <c r="AH40" s="12"/>
-      <c r="AI40" s="12"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13"/>
+      <c r="P40" s="15"/>
+      <c r="Q40" s="15"/>
+      <c r="R40" s="13"/>
+      <c r="S40" s="13"/>
+      <c r="T40" s="13"/>
+      <c r="U40" s="15"/>
+      <c r="V40" s="13"/>
+      <c r="W40" s="13"/>
+      <c r="X40" s="15"/>
+      <c r="Y40" s="13"/>
+      <c r="Z40" s="15"/>
+      <c r="AA40" s="13"/>
+      <c r="AB40" s="13"/>
+      <c r="AC40" s="13"/>
+      <c r="AD40" s="13"/>
+      <c r="AE40" s="13"/>
+      <c r="AF40" s="13"/>
+      <c r="AG40" s="13"/>
+      <c r="AH40" s="13"/>
+      <c r="AI40" s="13"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="D41" s="17" t="n">
+      <c r="D41" s="18" t="n">
         <v>46322</v>
       </c>
-      <c r="E41" s="17" t="n">
+      <c r="E41" s="18" t="n">
         <v>46324</v>
       </c>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
-      <c r="H41" s="16" t="n">
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17" t="n">
         <f aca="false">NETWORKDAYS(D41,E41,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I41" s="29" t="s">
+      <c r="I41" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="J41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="16"/>
-      <c r="O41" s="16"/>
-      <c r="P41" s="19"/>
-      <c r="Q41" s="19"/>
-      <c r="R41" s="16"/>
-      <c r="S41" s="16"/>
-      <c r="T41" s="16"/>
-      <c r="U41" s="19"/>
-      <c r="V41" s="16"/>
-      <c r="W41" s="16"/>
-      <c r="X41" s="19"/>
-      <c r="Y41" s="16"/>
-      <c r="Z41" s="19"/>
-      <c r="AA41" s="32"/>
-      <c r="AB41" s="32"/>
-      <c r="AC41" s="32"/>
-      <c r="AD41" s="16"/>
-      <c r="AE41" s="16"/>
-      <c r="AF41" s="16"/>
-      <c r="AG41" s="16"/>
-      <c r="AH41" s="16"/>
-      <c r="AI41" s="20"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20"/>
+      <c r="R41" s="17"/>
+      <c r="S41" s="17"/>
+      <c r="T41" s="17"/>
+      <c r="U41" s="20"/>
+      <c r="V41" s="17"/>
+      <c r="W41" s="17"/>
+      <c r="X41" s="20"/>
+      <c r="Y41" s="17"/>
+      <c r="Z41" s="20"/>
+      <c r="AA41" s="33"/>
+      <c r="AB41" s="33"/>
+      <c r="AC41" s="33"/>
+      <c r="AD41" s="17"/>
+      <c r="AE41" s="17"/>
+      <c r="AF41" s="17"/>
+      <c r="AG41" s="17"/>
+      <c r="AH41" s="17"/>
+      <c r="AI41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D42" s="17" t="n">
+      <c r="D42" s="18" t="n">
         <v>46325</v>
       </c>
-      <c r="E42" s="17" t="n">
+      <c r="E42" s="18" t="n">
         <v>46325</v>
       </c>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16" t="n">
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17" t="n">
         <f aca="false">NETWORKDAYS(D42,E42,Holidays!$A$2:$A$1000)</f>
         <v>1</v>
       </c>
-      <c r="I42" s="29" t="s">
+      <c r="I42" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="J42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="19"/>
-      <c r="N42" s="16"/>
-      <c r="O42" s="16"/>
-      <c r="P42" s="19"/>
-      <c r="Q42" s="19"/>
-      <c r="R42" s="16"/>
-      <c r="S42" s="16"/>
-      <c r="T42" s="16"/>
-      <c r="U42" s="19"/>
-      <c r="V42" s="16"/>
-      <c r="W42" s="16"/>
-      <c r="X42" s="19"/>
-      <c r="Y42" s="16"/>
-      <c r="Z42" s="19"/>
-      <c r="AA42" s="16"/>
-      <c r="AB42" s="16"/>
-      <c r="AC42" s="16"/>
-      <c r="AD42" s="32"/>
-      <c r="AE42" s="16"/>
-      <c r="AF42" s="16"/>
-      <c r="AG42" s="16"/>
-      <c r="AH42" s="16"/>
-      <c r="AI42" s="20"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="20"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="20"/>
+      <c r="R42" s="17"/>
+      <c r="S42" s="17"/>
+      <c r="T42" s="17"/>
+      <c r="U42" s="20"/>
+      <c r="V42" s="17"/>
+      <c r="W42" s="17"/>
+      <c r="X42" s="20"/>
+      <c r="Y42" s="17"/>
+      <c r="Z42" s="20"/>
+      <c r="AA42" s="17"/>
+      <c r="AB42" s="17"/>
+      <c r="AC42" s="17"/>
+      <c r="AD42" s="33"/>
+      <c r="AE42" s="17"/>
+      <c r="AF42" s="17"/>
+      <c r="AG42" s="17"/>
+      <c r="AH42" s="17"/>
+      <c r="AI42" s="21"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="D43" s="17" t="n">
+      <c r="D43" s="18" t="n">
         <v>46329</v>
       </c>
-      <c r="E43" s="17" t="n">
+      <c r="E43" s="18" t="n">
         <v>46330</v>
       </c>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16" t="n">
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17" t="n">
         <f aca="false">NETWORKDAYS(D43,E43,Holidays!$A$2:$A$1000)</f>
         <v>2</v>
       </c>
-      <c r="I43" s="29" t="s">
+      <c r="I43" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="J43" s="16"/>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="19"/>
-      <c r="N43" s="16"/>
-      <c r="O43" s="16"/>
-      <c r="P43" s="19"/>
-      <c r="Q43" s="19"/>
-      <c r="R43" s="16"/>
-      <c r="S43" s="16"/>
-      <c r="T43" s="16"/>
-      <c r="U43" s="19"/>
-      <c r="V43" s="16"/>
-      <c r="W43" s="16"/>
-      <c r="X43" s="19"/>
-      <c r="Y43" s="16"/>
-      <c r="Z43" s="19"/>
-      <c r="AA43" s="16"/>
-      <c r="AB43" s="16"/>
-      <c r="AC43" s="16"/>
-      <c r="AD43" s="16"/>
-      <c r="AE43" s="16"/>
-      <c r="AF43" s="32"/>
-      <c r="AG43" s="32"/>
-      <c r="AH43" s="16"/>
-      <c r="AI43" s="20"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="20"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="20"/>
+      <c r="Q43" s="20"/>
+      <c r="R43" s="17"/>
+      <c r="S43" s="17"/>
+      <c r="T43" s="17"/>
+      <c r="U43" s="20"/>
+      <c r="V43" s="17"/>
+      <c r="W43" s="17"/>
+      <c r="X43" s="20"/>
+      <c r="Y43" s="17"/>
+      <c r="Z43" s="20"/>
+      <c r="AA43" s="17"/>
+      <c r="AB43" s="17"/>
+      <c r="AC43" s="17"/>
+      <c r="AD43" s="17"/>
+      <c r="AE43" s="17"/>
+      <c r="AF43" s="33"/>
+      <c r="AG43" s="33"/>
+      <c r="AH43" s="17"/>
+      <c r="AI43" s="21"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="D44" s="17" t="n">
+      <c r="D44" s="18" t="n">
         <v>46331</v>
       </c>
-      <c r="E44" s="17" t="n">
+      <c r="E44" s="18" t="n">
         <v>46331</v>
       </c>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="16" t="n">
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17" t="n">
         <f aca="false">NETWORKDAYS(D44,E44,Holidays!$A$2:$A$1000)</f>
         <v>1</v>
       </c>
-      <c r="I44" s="29" t="s">
+      <c r="I44" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="J44" s="16"/>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="19"/>
-      <c r="N44" s="16"/>
-      <c r="O44" s="16"/>
-      <c r="P44" s="19"/>
-      <c r="Q44" s="19"/>
-      <c r="R44" s="16"/>
-      <c r="S44" s="16"/>
-      <c r="T44" s="16"/>
-      <c r="U44" s="19"/>
-      <c r="V44" s="16"/>
-      <c r="W44" s="16"/>
-      <c r="X44" s="19"/>
-      <c r="Y44" s="16"/>
-      <c r="Z44" s="19"/>
-      <c r="AA44" s="16"/>
-      <c r="AB44" s="16"/>
-      <c r="AC44" s="16"/>
-      <c r="AD44" s="16"/>
-      <c r="AE44" s="16"/>
-      <c r="AF44" s="16"/>
-      <c r="AG44" s="16"/>
-      <c r="AH44" s="32"/>
-      <c r="AI44" s="20"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="20"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="20"/>
+      <c r="R44" s="17"/>
+      <c r="S44" s="17"/>
+      <c r="T44" s="17"/>
+      <c r="U44" s="20"/>
+      <c r="V44" s="17"/>
+      <c r="W44" s="17"/>
+      <c r="X44" s="20"/>
+      <c r="Y44" s="17"/>
+      <c r="Z44" s="20"/>
+      <c r="AA44" s="17"/>
+      <c r="AB44" s="17"/>
+      <c r="AC44" s="17"/>
+      <c r="AD44" s="17"/>
+      <c r="AE44" s="17"/>
+      <c r="AF44" s="17"/>
+      <c r="AG44" s="17"/>
+      <c r="AH44" s="33"/>
+      <c r="AI44" s="21"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M45" s="33"/>
-      <c r="P45" s="33"/>
-      <c r="Q45" s="33"/>
-      <c r="U45" s="33"/>
-      <c r="X45" s="33"/>
-      <c r="Z45" s="33"/>
+      <c r="M45" s="34"/>
+      <c r="P45" s="34"/>
+      <c r="Q45" s="34"/>
+      <c r="U45" s="34"/>
+      <c r="X45" s="34"/>
+      <c r="Z45" s="34"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="34" t="s">
+      <c r="A46" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="B46" s="34" t="s">
+      <c r="B46" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="C46" s="35"/>
-      <c r="D46" s="36" t="n">
+      <c r="C46" s="36"/>
+      <c r="D46" s="37" t="n">
         <v>46282</v>
       </c>
-      <c r="E46" s="36" t="n">
+      <c r="E46" s="37" t="n">
         <v>46331</v>
       </c>
-      <c r="F46" s="35"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="34" t="n">
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="35" t="n">
         <f aca="false">NETWORKDAYS(D46,E46,Holidays!$A$2:$A$1000)</f>
         <v>34</v>
       </c>
-      <c r="I46" s="35"/>
-      <c r="J46" s="35"/>
-      <c r="K46" s="35"/>
-      <c r="L46" s="35"/>
-      <c r="M46" s="37"/>
-      <c r="N46" s="35"/>
-      <c r="O46" s="35"/>
-      <c r="P46" s="37"/>
-      <c r="Q46" s="37"/>
-      <c r="R46" s="35"/>
-      <c r="S46" s="35"/>
-      <c r="T46" s="35"/>
-      <c r="U46" s="37"/>
-      <c r="V46" s="35"/>
-      <c r="W46" s="35"/>
-      <c r="X46" s="37"/>
-      <c r="Y46" s="35"/>
-      <c r="Z46" s="37"/>
-      <c r="AA46" s="35"/>
-      <c r="AB46" s="35"/>
-      <c r="AC46" s="35"/>
-      <c r="AD46" s="35"/>
-      <c r="AE46" s="35"/>
-      <c r="AF46" s="35"/>
-      <c r="AG46" s="35"/>
-      <c r="AH46" s="35"/>
-      <c r="AI46" s="35"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="36"/>
+      <c r="K46" s="36"/>
+      <c r="L46" s="36"/>
+      <c r="M46" s="38"/>
+      <c r="N46" s="36"/>
+      <c r="O46" s="36"/>
+      <c r="P46" s="38"/>
+      <c r="Q46" s="38"/>
+      <c r="R46" s="36"/>
+      <c r="S46" s="36"/>
+      <c r="T46" s="36"/>
+      <c r="U46" s="38"/>
+      <c r="V46" s="36"/>
+      <c r="W46" s="36"/>
+      <c r="X46" s="38"/>
+      <c r="Y46" s="36"/>
+      <c r="Z46" s="38"/>
+      <c r="AA46" s="36"/>
+      <c r="AB46" s="36"/>
+      <c r="AC46" s="36"/>
+      <c r="AD46" s="36"/>
+      <c r="AE46" s="36"/>
+      <c r="AF46" s="36"/>
+      <c r="AG46" s="36"/>
+      <c r="AH46" s="36"/>
+      <c r="AI46" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3489,31 +3493,31 @@
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>46276</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>46289</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>46307</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>46364</v>
       </c>
     </row>

--- a/gant/live/gantt_live.xlsx
+++ b/gant/live/gantt_live.xlsx
@@ -532,10 +532,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="@"/>
+    <numFmt numFmtId="167" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -768,7 +769,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -782,7 +783,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -825,7 +826,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -841,7 +842,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -917,11 +918,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="13" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1217,6 +1222,7 @@
       <c r="K3" s="3" t="n">
         <v>46303</v>
       </c>
+      <c r="L3" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
@@ -1721,7 +1727,9 @@
       <c r="F13" s="18" t="n">
         <v>46303</v>
       </c>
-      <c r="G13" s="17"/>
+      <c r="G13" s="18" t="n">
+        <v>46304</v>
+      </c>
       <c r="H13" s="17" t="n">
         <f aca="false">NETWORKDAYS(D13,E13,Holidays!$A$2:$A$1000)</f>
         <v>2</v>
@@ -1774,8 +1782,12 @@
       <c r="E14" s="18" t="n">
         <v>46304</v>
       </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
+      <c r="F14" s="18" t="n">
+        <v>46304</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>46304</v>
+      </c>
       <c r="H14" s="17" t="n">
         <f aca="false">NETWORKDAYS(D14,E14,Holidays!$A$2:$A$1000)</f>
         <v>2</v>
@@ -2104,14 +2116,18 @@
       <c r="E20" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
+      <c r="F20" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="G20" s="18" t="n">
+        <v>46313</v>
+      </c>
       <c r="H20" s="17" t="n">
         <f aca="false">NETWORKDAYS(D20,E20,Holidays!$A$2:$A$1000)</f>
         <v>5</v>
       </c>
-      <c r="I20" s="26" t="s">
-        <v>89</v>
+      <c r="I20" s="19" t="s">
+        <v>53</v>
       </c>
       <c r="J20" s="17"/>
       <c r="K20" s="17"/>
@@ -2158,8 +2174,12 @@
       <c r="E21" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
+      <c r="F21" s="18" t="n">
+        <v>46313</v>
+      </c>
+      <c r="G21" s="18" t="n">
+        <v>46315</v>
+      </c>
       <c r="H21" s="17" t="n">
         <f aca="false">NETWORKDAYS(D21,E21,Holidays!$A$2:$A$1000)</f>
         <v>5</v>
@@ -2308,7 +2328,7 @@
         <v>107</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="D24" s="18" t="n">
         <v>46308</v>
@@ -2316,8 +2336,12 @@
       <c r="E24" s="18" t="n">
         <v>46310</v>
       </c>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
+      <c r="F24" s="18" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G24" s="18" t="n">
+        <v>46308</v>
+      </c>
       <c r="H24" s="17" t="n">
         <f aca="false">NETWORKDAYS(D24,E24,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
@@ -2373,13 +2397,15 @@
       <c r="F25" s="18" t="n">
         <v>46310</v>
       </c>
-      <c r="G25" s="17"/>
+      <c r="G25" s="18" t="n">
+        <v>46314</v>
+      </c>
       <c r="H25" s="17" t="n">
         <f aca="false">NETWORKDAYS(D25,E25,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I25" s="27" t="s">
-        <v>102</v>
+      <c r="I25" s="19" t="s">
+        <v>53</v>
       </c>
       <c r="J25" s="17"/>
       <c r="K25" s="17"/>
@@ -3461,7 +3487,8 @@
       <c r="AI46" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="K3:L3"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="L5:P5"/>
     <mergeCell ref="Q5:T5"/>
@@ -3502,22 +3529,22 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="39" t="n">
         <v>46276</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="39" t="n">
         <v>46289</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="39" t="n">
         <v>46307</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="39" t="n">
         <v>46364</v>
       </c>
     </row>

--- a/gant/live/gantt_live.xlsx
+++ b/gant/live/gantt_live.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="159">
   <si>
     <t xml:space="preserve">PROJECT TITLE</t>
   </si>
@@ -313,9 +313,6 @@
   </si>
   <si>
     <t xml:space="preserve">OMIM: gene-disease relationship</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pending</t>
   </si>
   <si>
     <t xml:space="preserve">Output: Notes on the gene and the phenotype</t>
@@ -590,7 +587,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -635,14 +632,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8CBAD"/>
-        <bgColor rgb="FFFFE699"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
-        <bgColor rgb="FFF8CBAD"/>
+        <bgColor rgb="FFFFCC99"/>
       </patternFill>
     </fill>
     <fill>
@@ -769,7 +760,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -782,7 +773,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -878,7 +869,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -886,43 +889,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="11" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -980,7 +967,7 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFF8CBAD"/>
+      <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF2A78D6"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -2010,8 +1997,8 @@
         <f aca="false">NETWORKDAYS(D18,E18,Holidays!$A$2:$A$1000)</f>
         <v>5</v>
       </c>
-      <c r="I18" s="26" t="s">
-        <v>89</v>
+      <c r="I18" s="19" t="s">
+        <v>53</v>
       </c>
       <c r="J18" s="17"/>
       <c r="K18" s="17"/>
@@ -2039,15 +2026,15 @@
       <c r="AG18" s="17"/>
       <c r="AH18" s="17"/>
       <c r="AI18" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>91</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>92</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>65</v>
@@ -2097,15 +2084,15 @@
       <c r="AG19" s="17"/>
       <c r="AH19" s="17"/>
       <c r="AI19" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>94</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>95</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>69</v>
@@ -2155,15 +2142,15 @@
       <c r="AG20" s="17"/>
       <c r="AH20" s="17"/>
       <c r="AI20" s="21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>97</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>98</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>69</v>
@@ -2213,15 +2200,15 @@
       <c r="AG21" s="17"/>
       <c r="AH21" s="17"/>
       <c r="AI21" s="21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>100</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>101</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>82</v>
@@ -2240,8 +2227,8 @@
         <f aca="false">NETWORKDAYS(D22,E22,Holidays!$A$2:$A$1000)</f>
         <v>15</v>
       </c>
-      <c r="I22" s="27" t="s">
-        <v>102</v>
+      <c r="I22" s="26" t="s">
+        <v>101</v>
       </c>
       <c r="J22" s="24"/>
       <c r="K22" s="24"/>
@@ -2269,15 +2256,15 @@
       <c r="AG22" s="17"/>
       <c r="AH22" s="17"/>
       <c r="AI22" s="21" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>104</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>105</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="14" t="n">
@@ -2322,10 +2309,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" s="17" t="s">
         <v>106</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>107</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>52</v>
@@ -2356,9 +2343,9 @@
       <c r="N24" s="17"/>
       <c r="O24" s="17"/>
       <c r="P24" s="20"/>
-      <c r="Q24" s="28"/>
-      <c r="R24" s="29"/>
-      <c r="S24" s="29"/>
+      <c r="Q24" s="27"/>
+      <c r="R24" s="28"/>
+      <c r="S24" s="28"/>
       <c r="T24" s="17"/>
       <c r="U24" s="20"/>
       <c r="V24" s="17"/>
@@ -2375,15 +2362,15 @@
       <c r="AG24" s="17"/>
       <c r="AH24" s="17"/>
       <c r="AI24" s="21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" s="17" t="s">
         <v>109</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>110</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>76</v>
@@ -2416,9 +2403,9 @@
       <c r="P25" s="20"/>
       <c r="Q25" s="20"/>
       <c r="R25" s="17"/>
-      <c r="S25" s="29"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="28"/>
+      <c r="S25" s="28"/>
+      <c r="T25" s="28"/>
+      <c r="U25" s="27"/>
       <c r="V25" s="17"/>
       <c r="W25" s="17"/>
       <c r="X25" s="20"/>
@@ -2433,18 +2420,18 @@
       <c r="AG25" s="17"/>
       <c r="AH25" s="17"/>
       <c r="AI25" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="C26" s="17" t="s">
         <v>113</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>114</v>
       </c>
       <c r="D26" s="18" t="n">
         <v>46308</v>
@@ -2455,13 +2442,15 @@
       <c r="F26" s="18" t="n">
         <v>46310</v>
       </c>
-      <c r="G26" s="17"/>
+      <c r="G26" s="18" t="n">
+        <v>46316</v>
+      </c>
       <c r="H26" s="17" t="n">
         <f aca="false">NETWORKDAYS(D26,E26,Holidays!$A$2:$A$1000)</f>
         <v>5</v>
       </c>
-      <c r="I26" s="27" t="s">
-        <v>102</v>
+      <c r="I26" s="19" t="s">
+        <v>53</v>
       </c>
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
@@ -2470,11 +2459,11 @@
       <c r="N26" s="17"/>
       <c r="O26" s="17"/>
       <c r="P26" s="20"/>
-      <c r="Q26" s="28"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="28"/>
+      <c r="Q26" s="27"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
+      <c r="T26" s="28"/>
+      <c r="U26" s="27"/>
       <c r="V26" s="17"/>
       <c r="W26" s="17"/>
       <c r="X26" s="20"/>
@@ -2489,15 +2478,15 @@
       <c r="AG26" s="17"/>
       <c r="AH26" s="17"/>
       <c r="AI26" s="21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="17" t="s">
         <v>116</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>117</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>61</v>
@@ -2514,8 +2503,8 @@
         <f aca="false">NETWORKDAYS(D27,E27,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I27" s="30" t="s">
-        <v>118</v>
+      <c r="I27" s="29" t="s">
+        <v>117</v>
       </c>
       <c r="J27" s="17"/>
       <c r="K27" s="17"/>
@@ -2529,9 +2518,9 @@
       <c r="S27" s="17"/>
       <c r="T27" s="17"/>
       <c r="U27" s="20"/>
-      <c r="V27" s="29"/>
-      <c r="W27" s="29"/>
-      <c r="X27" s="28"/>
+      <c r="V27" s="28"/>
+      <c r="W27" s="28"/>
+      <c r="X27" s="27"/>
       <c r="Y27" s="17"/>
       <c r="Z27" s="20"/>
       <c r="AA27" s="17"/>
@@ -2543,18 +2532,18 @@
       <c r="AG27" s="17"/>
       <c r="AH27" s="17"/>
       <c r="AI27" s="21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="B28" s="17" t="s">
-        <v>121</v>
-      </c>
       <c r="C28" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D28" s="18" t="n">
         <v>46308</v>
@@ -2565,13 +2554,15 @@
       <c r="F28" s="18" t="n">
         <v>46310</v>
       </c>
-      <c r="G28" s="17"/>
+      <c r="G28" s="18" t="n">
+        <v>46316</v>
+      </c>
       <c r="H28" s="17" t="n">
         <f aca="false">NETWORKDAYS(D28,E28,Holidays!$A$2:$A$1000)</f>
         <v>5</v>
       </c>
-      <c r="I28" s="27" t="s">
-        <v>102</v>
+      <c r="I28" s="19" t="s">
+        <v>53</v>
       </c>
       <c r="J28" s="17"/>
       <c r="K28" s="17"/>
@@ -2580,11 +2571,11 @@
       <c r="N28" s="17"/>
       <c r="O28" s="17"/>
       <c r="P28" s="20"/>
-      <c r="Q28" s="28"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="29"/>
-      <c r="U28" s="28"/>
+      <c r="Q28" s="27"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="28"/>
+      <c r="U28" s="27"/>
       <c r="V28" s="17"/>
       <c r="W28" s="17"/>
       <c r="X28" s="20"/>
@@ -2599,15 +2590,15 @@
       <c r="AG28" s="17"/>
       <c r="AH28" s="17"/>
       <c r="AI28" s="21" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="17" t="s">
         <v>123</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>124</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>65</v>
@@ -2624,8 +2615,8 @@
         <f aca="false">NETWORKDAYS(D29,E29,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I29" s="30" t="s">
-        <v>118</v>
+      <c r="I29" s="29" t="s">
+        <v>117</v>
       </c>
       <c r="J29" s="17"/>
       <c r="K29" s="17"/>
@@ -2639,9 +2630,9 @@
       <c r="S29" s="17"/>
       <c r="T29" s="17"/>
       <c r="U29" s="20"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="28"/>
+      <c r="V29" s="28"/>
+      <c r="W29" s="28"/>
+      <c r="X29" s="27"/>
       <c r="Y29" s="17"/>
       <c r="Z29" s="20"/>
       <c r="AA29" s="17"/>
@@ -2653,15 +2644,15 @@
       <c r="AG29" s="17"/>
       <c r="AH29" s="17"/>
       <c r="AI29" s="21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B30" s="12" t="s">
         <v>126</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>127</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="14" t="n">
@@ -2706,10 +2697,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="17" t="s">
         <v>128</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>57</v>
@@ -2726,8 +2717,8 @@
         <f aca="false">NETWORKDAYS(D31,E31,Holidays!$A$2:$A$1000)</f>
         <v>1</v>
       </c>
-      <c r="I31" s="30" t="s">
-        <v>118</v>
+      <c r="I31" s="29" t="s">
+        <v>117</v>
       </c>
       <c r="J31" s="17"/>
       <c r="K31" s="17"/>
@@ -2741,7 +2732,7 @@
       <c r="S31" s="17"/>
       <c r="T31" s="17"/>
       <c r="U31" s="20"/>
-      <c r="V31" s="31"/>
+      <c r="V31" s="30"/>
       <c r="W31" s="17"/>
       <c r="X31" s="20"/>
       <c r="Y31" s="17"/>
@@ -2758,10 +2749,10 @@
     </row>
     <row r="32" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B32" s="17" t="s">
         <v>130</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>131</v>
       </c>
       <c r="C32" s="17" t="s">
         <v>82</v>
@@ -2778,8 +2769,8 @@
         <f aca="false">NETWORKDAYS(D32,E32,Holidays!$A$2:$A$1000)</f>
         <v>1</v>
       </c>
-      <c r="I32" s="30" t="s">
-        <v>118</v>
+      <c r="I32" s="29" t="s">
+        <v>117</v>
       </c>
       <c r="J32" s="17"/>
       <c r="K32" s="17"/>
@@ -2791,7 +2782,7 @@
       <c r="Q32" s="20"/>
       <c r="R32" s="17"/>
       <c r="S32" s="17"/>
-      <c r="T32" s="31"/>
+      <c r="T32" s="30"/>
       <c r="U32" s="20"/>
       <c r="V32" s="17"/>
       <c r="W32" s="17"/>
@@ -2807,15 +2798,15 @@
       <c r="AG32" s="17"/>
       <c r="AH32" s="17"/>
       <c r="AI32" s="21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="B33" s="17" t="s">
         <v>133</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>134</v>
       </c>
       <c r="C33" s="17" t="s">
         <v>82</v>
@@ -2832,8 +2823,8 @@
         <f aca="false">NETWORKDAYS(D33,E33,Holidays!$A$2:$A$1000)</f>
         <v>4</v>
       </c>
-      <c r="I33" s="30" t="s">
-        <v>118</v>
+      <c r="I33" s="29" t="s">
+        <v>117</v>
       </c>
       <c r="J33" s="17"/>
       <c r="K33" s="17"/>
@@ -2846,10 +2837,10 @@
       <c r="R33" s="17"/>
       <c r="S33" s="17"/>
       <c r="T33" s="17"/>
-      <c r="U33" s="32"/>
-      <c r="V33" s="31"/>
-      <c r="W33" s="31"/>
-      <c r="X33" s="32"/>
+      <c r="U33" s="31"/>
+      <c r="V33" s="30"/>
+      <c r="W33" s="30"/>
+      <c r="X33" s="31"/>
       <c r="Y33" s="17"/>
       <c r="Z33" s="20"/>
       <c r="AA33" s="17"/>
@@ -2864,13 +2855,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="B34" s="17" t="s">
-        <v>136</v>
-      </c>
       <c r="C34" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D34" s="18" t="n">
         <v>46315</v>
@@ -2884,8 +2875,8 @@
         <f aca="false">NETWORKDAYS(D34,E34,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I34" s="30" t="s">
-        <v>118</v>
+      <c r="I34" s="29" t="s">
+        <v>117</v>
       </c>
       <c r="J34" s="17"/>
       <c r="K34" s="17"/>
@@ -2899,9 +2890,9 @@
       <c r="S34" s="17"/>
       <c r="T34" s="17"/>
       <c r="U34" s="20"/>
-      <c r="V34" s="31"/>
-      <c r="W34" s="31"/>
-      <c r="X34" s="32"/>
+      <c r="V34" s="30"/>
+      <c r="W34" s="30"/>
+      <c r="X34" s="31"/>
       <c r="Y34" s="17"/>
       <c r="Z34" s="20"/>
       <c r="AA34" s="17"/>
@@ -2916,10 +2907,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="B35" s="17" t="s">
         <v>137</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>138</v>
       </c>
       <c r="C35" s="17" t="s">
         <v>76</v>
@@ -2936,8 +2927,8 @@
         <f aca="false">NETWORKDAYS(D35,E35,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I35" s="30" t="s">
-        <v>118</v>
+      <c r="I35" s="29" t="s">
+        <v>117</v>
       </c>
       <c r="J35" s="17"/>
       <c r="K35" s="17"/>
@@ -2951,9 +2942,9 @@
       <c r="S35" s="17"/>
       <c r="T35" s="17"/>
       <c r="U35" s="20"/>
-      <c r="V35" s="31"/>
-      <c r="W35" s="31"/>
-      <c r="X35" s="32"/>
+      <c r="V35" s="30"/>
+      <c r="W35" s="30"/>
+      <c r="X35" s="31"/>
       <c r="Y35" s="17"/>
       <c r="Z35" s="20"/>
       <c r="AA35" s="17"/>
@@ -2968,10 +2959,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B36" s="17" t="s">
         <v>139</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>140</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>65</v>
@@ -2988,8 +2979,8 @@
         <f aca="false">NETWORKDAYS(D36,E36,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I36" s="30" t="s">
-        <v>118</v>
+      <c r="I36" s="29" t="s">
+        <v>117</v>
       </c>
       <c r="J36" s="17"/>
       <c r="K36" s="17"/>
@@ -3003,9 +2994,9 @@
       <c r="S36" s="17"/>
       <c r="T36" s="17"/>
       <c r="U36" s="20"/>
-      <c r="V36" s="31"/>
-      <c r="W36" s="31"/>
-      <c r="X36" s="32"/>
+      <c r="V36" s="30"/>
+      <c r="W36" s="30"/>
+      <c r="X36" s="31"/>
       <c r="Y36" s="17"/>
       <c r="Z36" s="20"/>
       <c r="AA36" s="17"/>
@@ -3020,10 +3011,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="B37" s="17" t="s">
         <v>141</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>142</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>69</v>
@@ -3040,8 +3031,8 @@
         <f aca="false">NETWORKDAYS(D37,E37,Holidays!$A$2:$A$1000)</f>
         <v>2</v>
       </c>
-      <c r="I37" s="30" t="s">
-        <v>118</v>
+      <c r="I37" s="29" t="s">
+        <v>117</v>
       </c>
       <c r="J37" s="17"/>
       <c r="K37" s="17"/>
@@ -3057,8 +3048,8 @@
       <c r="U37" s="20"/>
       <c r="V37" s="17"/>
       <c r="W37" s="17"/>
-      <c r="X37" s="32"/>
-      <c r="Y37" s="31"/>
+      <c r="X37" s="31"/>
+      <c r="Y37" s="30"/>
       <c r="Z37" s="20"/>
       <c r="AA37" s="17"/>
       <c r="AB37" s="17"/>
@@ -3072,10 +3063,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B38" s="17" t="s">
         <v>143</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>144</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>57</v>
@@ -3092,8 +3083,8 @@
         <f aca="false">NETWORKDAYS(D38,E38,Holidays!$A$2:$A$1000)</f>
         <v>1</v>
       </c>
-      <c r="I38" s="30" t="s">
-        <v>118</v>
+      <c r="I38" s="29" t="s">
+        <v>117</v>
       </c>
       <c r="J38" s="17"/>
       <c r="K38" s="17"/>
@@ -3110,7 +3101,7 @@
       <c r="V38" s="17"/>
       <c r="W38" s="17"/>
       <c r="X38" s="20"/>
-      <c r="Y38" s="31"/>
+      <c r="Y38" s="30"/>
       <c r="Z38" s="20"/>
       <c r="AA38" s="17"/>
       <c r="AB38" s="17"/>
@@ -3124,10 +3115,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" s="17" t="s">
         <v>145</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>146</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>65</v>
@@ -3144,8 +3135,8 @@
         <f aca="false">NETWORKDAYS(D39,E39,Holidays!$A$2:$A$1000)</f>
         <v>1</v>
       </c>
-      <c r="I39" s="30" t="s">
-        <v>118</v>
+      <c r="I39" s="29" t="s">
+        <v>117</v>
       </c>
       <c r="J39" s="17"/>
       <c r="K39" s="17"/>
@@ -3163,7 +3154,7 @@
       <c r="W39" s="17"/>
       <c r="X39" s="20"/>
       <c r="Y39" s="17"/>
-      <c r="Z39" s="32"/>
+      <c r="Z39" s="31"/>
       <c r="AA39" s="17"/>
       <c r="AB39" s="17"/>
       <c r="AC39" s="17"/>
@@ -3176,10 +3167,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B40" s="12" t="s">
         <v>147</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>148</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="14" t="n">
@@ -3224,10 +3215,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="B41" s="17" t="s">
         <v>149</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>150</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>57</v>
@@ -3244,8 +3235,8 @@
         <f aca="false">NETWORKDAYS(D41,E41,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I41" s="30" t="s">
-        <v>118</v>
+      <c r="I41" s="29" t="s">
+        <v>117</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
@@ -3264,9 +3255,9 @@
       <c r="X41" s="20"/>
       <c r="Y41" s="17"/>
       <c r="Z41" s="20"/>
-      <c r="AA41" s="33"/>
-      <c r="AB41" s="33"/>
-      <c r="AC41" s="33"/>
+      <c r="AA41" s="32"/>
+      <c r="AB41" s="32"/>
+      <c r="AC41" s="32"/>
       <c r="AD41" s="17"/>
       <c r="AE41" s="17"/>
       <c r="AF41" s="17"/>
@@ -3276,10 +3267,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B42" s="17" t="s">
         <v>151</v>
-      </c>
-      <c r="B42" s="17" t="s">
-        <v>152</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>69</v>
@@ -3296,8 +3287,8 @@
         <f aca="false">NETWORKDAYS(D42,E42,Holidays!$A$2:$A$1000)</f>
         <v>1</v>
       </c>
-      <c r="I42" s="30" t="s">
-        <v>118</v>
+      <c r="I42" s="29" t="s">
+        <v>117</v>
       </c>
       <c r="J42" s="17"/>
       <c r="K42" s="17"/>
@@ -3319,7 +3310,7 @@
       <c r="AA42" s="17"/>
       <c r="AB42" s="17"/>
       <c r="AC42" s="17"/>
-      <c r="AD42" s="33"/>
+      <c r="AD42" s="32"/>
       <c r="AE42" s="17"/>
       <c r="AF42" s="17"/>
       <c r="AG42" s="17"/>
@@ -3328,10 +3319,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="B43" s="17" t="s">
         <v>153</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>154</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>57</v>
@@ -3348,8 +3339,8 @@
         <f aca="false">NETWORKDAYS(D43,E43,Holidays!$A$2:$A$1000)</f>
         <v>2</v>
       </c>
-      <c r="I43" s="30" t="s">
-        <v>118</v>
+      <c r="I43" s="29" t="s">
+        <v>117</v>
       </c>
       <c r="J43" s="17"/>
       <c r="K43" s="17"/>
@@ -3373,17 +3364,17 @@
       <c r="AC43" s="17"/>
       <c r="AD43" s="17"/>
       <c r="AE43" s="17"/>
-      <c r="AF43" s="33"/>
-      <c r="AG43" s="33"/>
+      <c r="AF43" s="32"/>
+      <c r="AG43" s="32"/>
       <c r="AH43" s="17"/>
       <c r="AI43" s="21"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="B44" s="17" t="s">
         <v>155</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>156</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>57</v>
@@ -3400,8 +3391,8 @@
         <f aca="false">NETWORKDAYS(D44,E44,Holidays!$A$2:$A$1000)</f>
         <v>1</v>
       </c>
-      <c r="I44" s="30" t="s">
-        <v>118</v>
+      <c r="I44" s="29" t="s">
+        <v>117</v>
       </c>
       <c r="J44" s="17"/>
       <c r="K44" s="17"/>
@@ -3427,64 +3418,64 @@
       <c r="AE44" s="17"/>
       <c r="AF44" s="17"/>
       <c r="AG44" s="17"/>
-      <c r="AH44" s="33"/>
+      <c r="AH44" s="32"/>
       <c r="AI44" s="21"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M45" s="34"/>
-      <c r="P45" s="34"/>
-      <c r="Q45" s="34"/>
-      <c r="U45" s="34"/>
-      <c r="X45" s="34"/>
-      <c r="Z45" s="34"/>
+      <c r="M45" s="33"/>
+      <c r="P45" s="33"/>
+      <c r="Q45" s="33"/>
+      <c r="U45" s="33"/>
+      <c r="X45" s="33"/>
+      <c r="Z45" s="33"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="35" t="s">
+      <c r="A46" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="B46" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="B46" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="C46" s="36"/>
-      <c r="D46" s="37" t="n">
+      <c r="C46" s="35"/>
+      <c r="D46" s="36" t="n">
         <v>46282</v>
       </c>
-      <c r="E46" s="37" t="n">
+      <c r="E46" s="36" t="n">
         <v>46331</v>
       </c>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="35" t="n">
+      <c r="F46" s="35"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="34" t="n">
         <f aca="false">NETWORKDAYS(D46,E46,Holidays!$A$2:$A$1000)</f>
         <v>34</v>
       </c>
-      <c r="I46" s="36"/>
-      <c r="J46" s="36"/>
-      <c r="K46" s="36"/>
-      <c r="L46" s="36"/>
-      <c r="M46" s="38"/>
-      <c r="N46" s="36"/>
-      <c r="O46" s="36"/>
-      <c r="P46" s="38"/>
-      <c r="Q46" s="38"/>
-      <c r="R46" s="36"/>
-      <c r="S46" s="36"/>
-      <c r="T46" s="36"/>
-      <c r="U46" s="38"/>
-      <c r="V46" s="36"/>
-      <c r="W46" s="36"/>
-      <c r="X46" s="38"/>
-      <c r="Y46" s="36"/>
-      <c r="Z46" s="38"/>
-      <c r="AA46" s="36"/>
-      <c r="AB46" s="36"/>
-      <c r="AC46" s="36"/>
-      <c r="AD46" s="36"/>
-      <c r="AE46" s="36"/>
-      <c r="AF46" s="36"/>
-      <c r="AG46" s="36"/>
-      <c r="AH46" s="36"/>
-      <c r="AI46" s="36"/>
+      <c r="I46" s="35"/>
+      <c r="J46" s="35"/>
+      <c r="K46" s="35"/>
+      <c r="L46" s="35"/>
+      <c r="M46" s="37"/>
+      <c r="N46" s="35"/>
+      <c r="O46" s="35"/>
+      <c r="P46" s="37"/>
+      <c r="Q46" s="37"/>
+      <c r="R46" s="35"/>
+      <c r="S46" s="35"/>
+      <c r="T46" s="35"/>
+      <c r="U46" s="37"/>
+      <c r="V46" s="35"/>
+      <c r="W46" s="35"/>
+      <c r="X46" s="37"/>
+      <c r="Y46" s="35"/>
+      <c r="Z46" s="37"/>
+      <c r="AA46" s="35"/>
+      <c r="AB46" s="35"/>
+      <c r="AC46" s="35"/>
+      <c r="AD46" s="35"/>
+      <c r="AE46" s="35"/>
+      <c r="AF46" s="35"/>
+      <c r="AG46" s="35"/>
+      <c r="AH46" s="35"/>
+      <c r="AI46" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3525,26 +3516,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="39" t="n">
+      <c r="A2" s="38" t="n">
         <v>46276</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="39" t="n">
+      <c r="A3" s="38" t="n">
         <v>46289</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="39" t="n">
+      <c r="A4" s="38" t="n">
         <v>46307</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="39" t="n">
+      <c r="A5" s="38" t="n">
         <v>46364</v>
       </c>
     </row>

--- a/gant/live/gantt_live.xlsx
+++ b/gant/live/gantt_live.xlsx
@@ -399,25 +399,25 @@
     <t xml:space="preserve">Figures</t>
   </si>
   <si>
+    <t xml:space="preserve">Output: Figures in figures/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evolutionary and homolog interpretation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Output: Interpretation notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limitations of each analysis</t>
+  </si>
+  <si>
     <t xml:space="preserve">Backlog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Output: Figures in figures/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evolutionary and homolog interpretation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Output: Interpretation notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limitations of each analysis</t>
   </si>
   <si>
     <t xml:space="preserve">Output: Limitations summary (to be integrated into the Discussion section)</t>
@@ -2497,14 +2497,16 @@
       <c r="E27" s="18" t="n">
         <v>46317</v>
       </c>
-      <c r="F27" s="17"/>
+      <c r="F27" s="18" t="n">
+        <v>46317</v>
+      </c>
       <c r="G27" s="17"/>
       <c r="H27" s="17" t="n">
         <f aca="false">NETWORKDAYS(D27,E27,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I27" s="29" t="s">
-        <v>117</v>
+      <c r="I27" s="26" t="s">
+        <v>101</v>
       </c>
       <c r="J27" s="17"/>
       <c r="K27" s="17"/>
@@ -2532,15 +2534,15 @@
       <c r="AG27" s="17"/>
       <c r="AH27" s="17"/>
       <c r="AI27" s="21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="B28" s="17" t="s">
         <v>119</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>120</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>113</v>
@@ -2590,15 +2592,15 @@
       <c r="AG28" s="17"/>
       <c r="AH28" s="17"/>
       <c r="AI28" s="21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B29" s="17" t="s">
         <v>122</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>123</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>65</v>
@@ -2616,7 +2618,7 @@
         <v>3</v>
       </c>
       <c r="I29" s="29" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J29" s="17"/>
       <c r="K29" s="17"/>
@@ -2718,7 +2720,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="29" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J31" s="17"/>
       <c r="K31" s="17"/>
@@ -2770,7 +2772,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="29" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J32" s="17"/>
       <c r="K32" s="17"/>
@@ -2824,7 +2826,7 @@
         <v>4</v>
       </c>
       <c r="I33" s="29" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J33" s="17"/>
       <c r="K33" s="17"/>
@@ -2869,14 +2871,16 @@
       <c r="E34" s="18" t="n">
         <v>46317</v>
       </c>
-      <c r="F34" s="17"/>
+      <c r="F34" s="18" t="n">
+        <v>46316</v>
+      </c>
       <c r="G34" s="17"/>
       <c r="H34" s="17" t="n">
         <f aca="false">NETWORKDAYS(D34,E34,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I34" s="29" t="s">
-        <v>117</v>
+      <c r="I34" s="26" t="s">
+        <v>101</v>
       </c>
       <c r="J34" s="17"/>
       <c r="K34" s="17"/>
@@ -2928,7 +2932,7 @@
         <v>3</v>
       </c>
       <c r="I35" s="29" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J35" s="17"/>
       <c r="K35" s="17"/>
@@ -2980,7 +2984,7 @@
         <v>3</v>
       </c>
       <c r="I36" s="29" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J36" s="17"/>
       <c r="K36" s="17"/>
@@ -3032,7 +3036,7 @@
         <v>2</v>
       </c>
       <c r="I37" s="29" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J37" s="17"/>
       <c r="K37" s="17"/>
@@ -3084,7 +3088,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="29" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J38" s="17"/>
       <c r="K38" s="17"/>
@@ -3136,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="29" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J39" s="17"/>
       <c r="K39" s="17"/>
@@ -3236,7 +3240,7 @@
         <v>3</v>
       </c>
       <c r="I41" s="29" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
@@ -3288,7 +3292,7 @@
         <v>1</v>
       </c>
       <c r="I42" s="29" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J42" s="17"/>
       <c r="K42" s="17"/>
@@ -3340,7 +3344,7 @@
         <v>2</v>
       </c>
       <c r="I43" s="29" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J43" s="17"/>
       <c r="K43" s="17"/>
@@ -3392,7 +3396,7 @@
         <v>1</v>
       </c>
       <c r="I44" s="29" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J44" s="17"/>
       <c r="K44" s="17"/>

--- a/gant/live/gantt_live.xlsx
+++ b/gant/live/gantt_live.xlsx
@@ -2819,14 +2819,16 @@
       <c r="E33" s="18" t="n">
         <v>46317</v>
       </c>
-      <c r="F33" s="17"/>
+      <c r="F33" s="18" t="n">
+        <v>46317</v>
+      </c>
       <c r="G33" s="17"/>
       <c r="H33" s="17" t="n">
         <f aca="false">NETWORKDAYS(D33,E33,Holidays!$A$2:$A$1000)</f>
         <v>4</v>
       </c>
-      <c r="I33" s="29" t="s">
-        <v>123</v>
+      <c r="I33" s="26" t="s">
+        <v>101</v>
       </c>
       <c r="J33" s="17"/>
       <c r="K33" s="17"/>
@@ -2925,14 +2927,16 @@
       <c r="E35" s="18" t="n">
         <v>46317</v>
       </c>
-      <c r="F35" s="17"/>
+      <c r="F35" s="18" t="n">
+        <v>46316</v>
+      </c>
       <c r="G35" s="17"/>
       <c r="H35" s="17" t="n">
         <f aca="false">NETWORKDAYS(D35,E35,Holidays!$A$2:$A$1000)</f>
         <v>3</v>
       </c>
-      <c r="I35" s="29" t="s">
-        <v>123</v>
+      <c r="I35" s="26" t="s">
+        <v>101</v>
       </c>
       <c r="J35" s="17"/>
       <c r="K35" s="17"/>
